--- a/RoundIntroductions.xlsx
+++ b/RoundIntroductions.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97839D52-519E-4C51-BBC4-04C6AFFA2D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81CBBED0-AAE0-40FC-9F17-8D1515B8DA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="255">
   <si>
     <t>Round</t>
   </si>
@@ -67,16 +67,16 @@
     <t>SDG 3: Good Health and Well-Being</t>
   </si>
   <si>
-    <t>This round focuses on SDG 3. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
-  </si>
-  <si>
-    <t>Recognise the goal in daily work</t>
-  </si>
-  <si>
-    <t>Connect choices to real impact</t>
-  </si>
-  <si>
-    <t>Turn awareness into action</t>
+    <t>SDG 3 is about enabling healthy lives and well-being for people of all ages. It covers prevention, accessible healthcare, mental well-being and safer living and working conditions. In a company, this also means preventing accidents, limiting exposure to hazardous substances and building a culture in which people report risks and learn from near misses. STOCKMEIER links this theme to its Zero in Focus ambition: zero work-related accidents and zero harmful effects on employees’ health. The sustainability report describes audited health and safety systems, employee training and practical safety improvements. This round explores how daily choices, clear procedures and shared responsibility turn health and safety into a sustainable way of working.</t>
+  </si>
+  <si>
+    <t>Healthy lives and mental well-being</t>
+  </si>
+  <si>
+    <t>Safe working conditions and prevention</t>
+  </si>
+  <si>
+    <t>Access to care, knowledge and protection</t>
   </si>
   <si>
     <t>Start the questions</t>
@@ -88,16 +88,16 @@
     <t>SDG 3: Goede gezondheid en welzijn</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 3. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
-  </si>
-  <si>
-    <t>Herken het doel in je dagelijkse werk</t>
-  </si>
-  <si>
-    <t>Koppel keuzes aan echte impact</t>
-  </si>
-  <si>
-    <t>Zet bewustwording om in actie</t>
+    <t>SDG 3 draait om een gezond leven en welzijn voor mensen van alle leeftijden. Het doel gaat over preventie, toegankelijke zorg, mentaal welzijn en veilige leef- en werkomstandigheden. Binnen een bedrijf betekent dit onder meer ongevallen voorkomen, blootstelling aan gevaarlijke stoffen beperken en een cultuur creëren waarin risico’s en bijna-ongevallen worden gemeld. STOCKMEIER koppelt dit aan de ambitie Zero in Focus: nul werkgerelateerde ongevallen en nul schadelijke gevolgen voor de gezondheid. Het duurzaamheidsrapport beschrijft gecontroleerde veiligheidsmanagementsystemen, trainingen en praktische verbeteringen op de werkvloer. In deze ronde ontdek je hoe dagelijkse keuzes, duidelijke procedures en gezamenlijke verantwoordelijkheid bijdragen aan een gezonde en veilige werkomgeving.</t>
+  </si>
+  <si>
+    <t>Gezondheid en mentaal welzijn</t>
+  </si>
+  <si>
+    <t>Veilig werken en risico’s voorkomen</t>
+  </si>
+  <si>
+    <t>Toegang tot zorg, kennis en bescherming</t>
   </si>
   <si>
     <t>Start de vragen</t>
@@ -202,13 +202,31 @@
     <t>SDG 4: Quality Education</t>
   </si>
   <si>
-    <t>This round focuses on SDG 4. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 4 aims to ensure inclusive and equitable quality education and lifelong learning opportunities for everyone. Education is not limited to schools: organisations also need people who can keep learning, share knowledge and develop the skills required for safer and more sustainable work. Training helps employees understand procedures, recognise environmental and social risks and contribute ideas for improvement. STOCKMEIER’s report highlights regular training, sustainability information sessions and the international YouPro programme, in which young professionals learn across countries and work on practical sustainability projects. This round focuses on how accessible learning, professional development and knowledge sharing strengthen both individuals and the organisation, and help turn sustainability ambitions into everyday action.</t>
+  </si>
+  <si>
+    <t>Inclusive access to learning</t>
+  </si>
+  <si>
+    <t>Skills for work and sustainable development</t>
+  </si>
+  <si>
+    <t>Lifelong learning and knowledge sharing</t>
   </si>
   <si>
     <t>SDG 4: Kwaliteitsonderwijs</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 4. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 4 wil inclusief en gelijkwaardig kwaliteitsonderwijs en mogelijkheden voor een leven lang leren voor iedereen realiseren. Onderwijs speelt niet alleen op school: ook organisaties hebben mensen nodig die blijven leren, kennis delen en vaardigheden ontwikkelen voor veiliger en duurzamer werk. Training helpt medewerkers om procedures te begrijpen, milieu- en sociale risico’s te herkennen en verbetervoorstellen te doen. Het duurzaamheidsrapport van STOCKMEIER noemt periodieke trainingen, informatiesessies over duurzaamheid en het internationale YouPro-programma, waarin jonge professionals over landsgrenzen heen leren en aan praktische duurzaamheidsprojecten werken. In deze ronde staat centraal hoe toegankelijk leren, persoonlijke ontwikkeling en kennisdeling zowel mensen als de organisatie sterker maken en duurzaamheidsambities vertalen naar dagelijks handelen.</t>
+  </si>
+  <si>
+    <t>Toegankelijke en inclusieve leermogelijkheden</t>
+  </si>
+  <si>
+    <t>Vaardigheden voor werk en duurzame ontwikkeling</t>
+  </si>
+  <si>
+    <t>Een leven lang leren en kennis delen</t>
   </si>
   <si>
     <t>ODD 4 : Quality Education</t>
@@ -235,13 +253,31 @@
     <t>SDG 5: Gender Equality</t>
   </si>
   <si>
-    <t>This round focuses on SDG 5. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 5 seeks gender equality and equal opportunities for women and girls. It addresses discrimination, equal participation, leadership opportunities, fair access to resources and the removal of barriers that restrict development. In the workplace, this means transparent career paths, equal treatment, an inclusive culture and attention to differences in representation and pay. STOCKMEIER’s sustainability report describes diversity and equal opportunity as important parts of its culture and highlights WOMEN@STOCKMEIER, a network that supports professional development, exchange and visibility. This round examines why equality is more than a policy: it depends on everyday decisions, respectful collaboration and working conditions in which talent can develop regardless of gender.</t>
+  </si>
+  <si>
+    <t>Equal rights, treatment and pay</t>
+  </si>
+  <si>
+    <t>Participation and leadership opportunities</t>
+  </si>
+  <si>
+    <t>An inclusive culture without barriers</t>
   </si>
   <si>
     <t>SDG 5: Gendergelijkheid</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 5. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 5 richt zich op gendergelijkheid en gelijke kansen voor vrouwen en meisjes. Het doel gaat over het tegengaan van discriminatie, gelijkwaardige deelname, kansen op leiderschap, eerlijke toegang tot middelen en het wegnemen van belemmeringen in ontwikkeling. Op het werk betekent dit transparante loopbaanpaden, gelijke behandeling, een inclusieve cultuur en aandacht voor verschillen in vertegenwoordiging en beloning. Het duurzaamheidsrapport van STOCKMEIER beschrijft diversiteit en gelijke kansen als belangrijke onderdelen van de bedrijfscultuur en benoemt WOMEN@STOCKMEIER, een netwerk voor professionele ontwikkeling, uitwisseling en zichtbaarheid. In deze ronde ontdek je waarom gelijkheid meer is dan beleid: het vraagt om bewuste dagelijkse keuzes, respectvolle samenwerking en omstandigheden waarin talent zich onafhankelijk van gender kan ontwikkelen.</t>
+  </si>
+  <si>
+    <t>Gelijke rechten, behandeling en beloning</t>
+  </si>
+  <si>
+    <t>Deelname en kansen op leiderschap</t>
+  </si>
+  <si>
+    <t>Een inclusieve cultuur zonder barrières</t>
   </si>
   <si>
     <t>ODD 5 : Gender Equality</t>
@@ -268,13 +304,31 @@
     <t>SDG 6: Clean Water and Sanitation</t>
   </si>
   <si>
-    <t>This round focuses on SDG 6. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 6 is about clean water, sanitation and the sustainable management of water resources. Water is essential for people, ecosystems and industrial processes, but availability and quality are under pressure. Responsible water management therefore includes reducing withdrawals, preventing pollution, treating wastewater safely and understanding local water stress. STOCKMEIER uses water in activities such as blending, cleaning and formulation and has assessed production sites with the Aqueduct Water Risk Atlas. The sustainability report also refers to recycling initiatives, water-saving technologies, rainwater infiltration and soil protection. This round shows how careful handling, monitoring and site-specific measures help protect water throughout the value chain and preserve this fundamental resource for future generations.</t>
+  </si>
+  <si>
+    <t>Safe and sufficient water</t>
+  </si>
+  <si>
+    <t>Prevent pollution and protect ecosystems</t>
+  </si>
+  <si>
+    <t>Use, treat and reuse water efficiently</t>
   </si>
   <si>
     <t>SDG 6: Schoon water en sanitair</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 6. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 6 gaat over schoon water, sanitair en het duurzaam beheren van waterbronnen. Water is onmisbaar voor mensen, ecosystemen en industriële processen, maar beschikbaarheid en kwaliteit staan onder druk. Verantwoord waterbeheer betekent daarom wateronttrekking beperken, vervuiling voorkomen, afvalwater veilig behandelen en lokale waterstress begrijpen. STOCKMEIER gebruikt water onder meer bij mengen, reinigen en formuleren en heeft productielocaties beoordeeld met de Aqueduct Water Risk Atlas. Het duurzaamheidsrapport noemt daarnaast recyclinginitiatieven, waterbesparende technologie, regenwaterinfiltratie en bodembescherming. In deze ronde ontdek je hoe zorgvuldig omgaan met water, goede monitoring en locatiespecifieke maatregelen helpen om water in de hele waardeketen te beschermen en deze onmisbare hulpbron voor toekomstige generaties te behouden.</t>
+  </si>
+  <si>
+    <t>Veilig en voldoende water</t>
+  </si>
+  <si>
+    <t>Vervuiling voorkomen en ecosystemen beschermen</t>
+  </si>
+  <si>
+    <t>Water efficiënt gebruiken, behandelen en hergebruiken</t>
   </si>
   <si>
     <t>ODD 6 : Clean Water and Sanitation</t>
@@ -301,13 +355,31 @@
     <t>SDG 7: Affordable and Clean Energy</t>
   </si>
   <si>
-    <t>This round focuses on SDG 7. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 7 focuses on access to affordable, reliable and sustainable energy. Energy enables transport, production and everyday life, but fossil energy also contributes to greenhouse gas emissions. The transition requires improved energy efficiency, more renewable electricity and technologies that reduce dependence on fossil fuels. STOCKMEIER’s report describes renewable electricity, photovoltaic installations and the expansion of electric mobility as parts of its decarbonisation approach. Energy use and emissions are monitored through recognised frameworks, helping the Group identify where improvement is possible. This round explores how choices about electricity, fuels, equipment and mobility affect both climate impact and operational resilience, and why saving energy is often the first practical step toward cleaner energy use.</t>
+  </si>
+  <si>
+    <t>Reliable and affordable energy</t>
+  </si>
+  <si>
+    <t>Energy efficiency and lower consumption</t>
+  </si>
+  <si>
+    <t>Renewable energy and cleaner technology</t>
   </si>
   <si>
     <t>SDG 7: Betaalbare en duurzame energie</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 7. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 7 richt zich op toegang tot betaalbare, betrouwbare en duurzame energie. Energie maakt transport, productie en het dagelijks leven mogelijk, maar fossiele energie veroorzaakt ook broeikasgasuitstoot. De overgang vraagt om hogere energie-efficiëntie, meer hernieuwbare elektriciteit en technologieën die de afhankelijkheid van fossiele brandstoffen verminderen. Het duurzaamheidsrapport van STOCKMEIER beschrijft hernieuwbare elektriciteit, zonnepanelen en de uitbreiding van elektrische mobiliteit als onderdelen van de aanpak voor verduurzaming. Energiegebruik en emissies worden via erkende kaders gemonitord, zodat duidelijk wordt waar verbetering mogelijk is. In deze ronde ontdek je hoe keuzes rond elektriciteit, brandstoffen, apparatuur en mobiliteit zowel de klimaatimpact als de bedrijfszekerheid beïnvloeden, en waarom energie besparen vaak de eerste praktische stap naar schoner energiegebruik is.</t>
+  </si>
+  <si>
+    <t>Betrouwbare en betaalbare energie</t>
+  </si>
+  <si>
+    <t>Energie-efficiëntie en lager verbruik</t>
+  </si>
+  <si>
+    <t>Hernieuwbare energie en schonere technologie</t>
   </si>
   <si>
     <t>ODD 7 : Affordable and Clean Energy</t>
@@ -334,13 +406,31 @@
     <t>SDG 8: Decent Work and Economic Growth</t>
   </si>
   <si>
-    <t>This round focuses on SDG 8. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 8 promotes inclusive and sustainable economic growth, productive employment and decent work for everyone. Growth is sustainable only when it respects labour rights, creates safe workplaces, supports fair pay and uses resources more efficiently. It also requires opportunities for young people, innovation and responsible supply chains without forced labour or exploitation. STOCKMEIER’s report connects this theme to occupational safety, employee development, collective bargaining, minimum wage requirements and supply-chain risk assessments. Its Zero in Focus approach includes preventing work-related accidents and human-rights violations. This round examines how organisations can combine economic performance with safe, fair and meaningful work, and why decent working conditions are essential for resilient operations and long-term value creation.</t>
+  </si>
+  <si>
+    <t>Safe work and protected labour rights</t>
+  </si>
+  <si>
+    <t>Fair opportunities, pay and development</t>
+  </si>
+  <si>
+    <t>Sustainable growth and resource efficiency</t>
   </si>
   <si>
     <t>SDG 8: Waardig werk en economische groei</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 8. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 8 bevordert inclusieve en duurzame economische groei, productieve werkgelegenheid en waardig werk voor iedereen. Groei is pas duurzaam wanneer arbeidsrechten worden gerespecteerd, werkplekken veilig zijn, mensen eerlijk worden beloond en grondstoffen efficiënter worden gebruikt. Het doel vraagt ook om kansen voor jongeren, innovatie en verantwoorde ketens zonder dwangarbeid of uitbuiting. Het duurzaamheidsrapport van STOCKMEIER verbindt dit thema aan arbeidsveiligheid, ontwikkeling van medewerkers, cao-afspraken, minimumlooneisen en risicoanalyses in de toeleveringsketen. Zero in Focus omvat daarbij het voorkomen van werkgerelateerde ongevallen en mensenrechtenschendingen. In deze ronde ontdek je hoe economische prestaties samengaan met veilig, eerlijk en betekenisvol werk en waarom goede arbeidsomstandigheden noodzakelijk zijn voor continuïteit en waardecreatie op lange termijn.</t>
+  </si>
+  <si>
+    <t>Veilig werk en beschermde arbeidsrechten</t>
+  </si>
+  <si>
+    <t>Eerlijke kansen, beloning en ontwikkeling</t>
+  </si>
+  <si>
+    <t>Duurzame groei en efficiënt grondstoffengebruik</t>
   </si>
   <si>
     <t>ODD 8 : Decent Work and Economic Growth</t>
@@ -367,13 +457,31 @@
     <t>SDG 9: Industry, Innovation and Infrastructure</t>
   </si>
   <si>
-    <t>This round focuses on SDG 9. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 9 concerns resilient infrastructure, sustainable industrialisation and innovation. Reliable sites, transport networks, digital systems and production technology are essential for delivering products safely and efficiently. At the same time, industry must reduce resource use and emissions and become more resilient to climate and supply-chain disruption. Innovation can improve processes, enable cleaner technologies and turn local ideas into scalable solutions. STOCKMEIER’s report provides examples such as photovoltaic energy, electric mobility, emission-control equipment and cross-site reuse of materials. This round explores how investment, technical improvement and collaboration can make infrastructure stronger and industry more sustainable, while maintaining safety, quality and continuity for customers and communities.</t>
+  </si>
+  <si>
+    <t>Reliable and resilient infrastructure</t>
+  </si>
+  <si>
+    <t>Cleaner and more efficient industry</t>
+  </si>
+  <si>
+    <t>Innovation through technology and collaboration</t>
   </si>
   <si>
     <t>SDG 9: Industrie, innovatie en infrastructuur</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 9. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 9 gaat over veerkrachtige infrastructuur, duurzame industrialisatie en innovatie. Betrouwbare locaties, transportnetwerken, digitale systemen en productietechnologie zijn noodzakelijk om producten veilig en efficiënt te leveren. Tegelijk moet de industrie grondstoffen en emissies verminderen en beter bestand worden tegen klimaat- en ketenverstoringen. Innovatie kan processen verbeteren, schonere technologie mogelijk maken en lokale ideeën opschalen. In het duurzaamheidsrapport van STOCKMEIER staan voorbeelden zoals zonnepanelen, elektrische mobiliteit, installaties voor emissiebeheersing en hergebruik van materialen tussen locaties. In deze ronde ontdek je hoe investeringen, technische verbeteringen en samenwerking infrastructuur sterker en industrie duurzamer maken, terwijl veiligheid, kwaliteit en continuïteit voor klanten en gemeenschappen behouden blijven.</t>
+  </si>
+  <si>
+    <t>Betrouwbare en veerkrachtige infrastructuur</t>
+  </si>
+  <si>
+    <t>Schonere en efficiëntere industrie</t>
+  </si>
+  <si>
+    <t>Innovatie door technologie en samenwerking</t>
   </si>
   <si>
     <t>ODD 9 : Industry, Innovation and Infrastructure</t>
@@ -400,13 +508,31 @@
     <t>SDG 10: Reduced Inequalities</t>
   </si>
   <si>
-    <t>This round focuses on SDG 10. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 10 aims to reduce inequality within and between countries. It calls for social, economic and political inclusion, equal opportunity and the removal of discriminatory practices. In organisations, inequality can appear through barriers to recruitment, development, pay, leadership or participation. A diverse workforce creates value only when people are respected, heard and given realistic opportunities to contribute. STOCKMEIER’s report identifies diversity, inclusion, fair treatment and human rights as important elements of its social and governance approach, supported by codes of conduct and employee networks. This round focuses on recognising unequal outcomes, making decisions more inclusive and creating working conditions in which differences do not determine a person’s access to opportunity, safety or professional growth.</t>
+  </si>
+  <si>
+    <t>Social and economic inclusion</t>
+  </si>
+  <si>
+    <t>Equal opportunities without discrimination</t>
+  </si>
+  <si>
+    <t>Participation, respect and accessibility</t>
   </si>
   <si>
     <t>SDG 10: Ongelijkheid verminderen</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 10. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 10 wil ongelijkheid binnen en tussen landen verminderen. Het doel vraagt om sociale, economische en politieke inclusie, gelijke kansen en het wegnemen van discriminerende praktijken. In organisaties kan ongelijkheid zichtbaar worden in belemmeringen bij werving, ontwikkeling, beloning, leiderschap of deelname. Een divers personeelsbestand levert pas echt waarde op wanneer mensen worden gerespecteerd, gehoord en daadwerkelijk kunnen bijdragen. Het duurzaamheidsrapport van STOCKMEIER benoemt diversiteit, inclusie, eerlijke behandeling en mensenrechten als belangrijke onderdelen van de sociale en bestuurlijke aanpak, ondersteund door gedragscodes en medewerkersnetwerken. In deze ronde ontdek je hoe je ongelijke uitkomsten herkent, besluitvorming inclusiever maakt en omstandigheden creëert waarin verschillen niet bepalen welke kansen, veiligheid of professionele groei iemand krijgt.</t>
+  </si>
+  <si>
+    <t>Sociale en economische inclusie</t>
+  </si>
+  <si>
+    <t>Gelijke kansen zonder discriminatie</t>
+  </si>
+  <si>
+    <t>Deelname, respect en toegankelijkheid</t>
   </si>
   <si>
     <t>ODD 10 : Reduced Inequalities</t>
@@ -433,13 +559,31 @@
     <t>SDG 11: Sustainable Cities and Communities</t>
   </si>
   <si>
-    <t>This round focuses on SDG 11. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 11 is about making cities and communities inclusive, safe, resilient and sustainable. Businesses are part of those communities through their sites, transport movements, use of space and response to local risks. Sustainable communities need safe infrastructure, reduced environmental impact, emergency preparedness and cooperation between companies and public services. STOCKMEIER’s report describes support during severe flooding, including logistics, water treatment and the supply of disinfectant, as well as efforts to understand physical climate risks to sites and supply chains. This round explores how responsible operations, preparedness and local cooperation can protect people and the environment, strengthen continuity and help communities respond to extreme weather and other disruptions.</t>
+  </si>
+  <si>
+    <t>Safe, inclusive and resilient communities</t>
+  </si>
+  <si>
+    <t>Preparedness for climate and disaster risks</t>
+  </si>
+  <si>
+    <t>Responsible sites, logistics and local cooperation</t>
   </si>
   <si>
     <t>SDG 11: Duurzame steden en gemeenschappen</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 11. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 11 gaat over inclusieve, veilige, veerkrachtige en duurzame steden en gemeenschappen. Bedrijven maken deel uit van die gemeenschappen via hun locaties, transportbewegingen, ruimtegebruik en reactie op lokale risico’s. Duurzame gemeenschappen hebben veilige infrastructuur, minder milieubelasting, goede noodvoorbereiding en samenwerking tussen bedrijven en publieke diensten nodig. Het duurzaamheidsrapport van STOCKMEIER beschrijft ondersteuning bij ernstige overstromingen, waaronder logistiek, waterbehandeling en levering van desinfectiemiddel. Ook worden fysieke klimaatrisico’s voor locaties en ketens onderzocht. In deze ronde ontdek je hoe verantwoord ondernemen, voorbereiding en lokale samenwerking mensen en milieu beschermen, bedrijfscontinuïteit versterken en gemeenschappen helpen omgaan met extreem weer en andere verstoringen.</t>
+  </si>
+  <si>
+    <t>Veilige, inclusieve en veerkrachtige gemeenschappen</t>
+  </si>
+  <si>
+    <t>Voorbereiding op klimaat- en rampenrisico’s</t>
+  </si>
+  <si>
+    <t>Verantwoorde locaties, logistiek en lokale samenwerking</t>
   </si>
   <si>
     <t>ODD 11 : Sustainable Cities and Communities</t>
@@ -466,13 +610,31 @@
     <t>SDG 12: Responsible Consumption and Production</t>
   </si>
   <si>
-    <t>This round focuses on SDG 12. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 12 focuses on producing and consuming with fewer resources, less waste and better control of chemicals throughout their life cycle. It promotes efficient material use, prevention, reuse, recycling, responsible procurement and transparent sustainability reporting. This is especially relevant in chemical distribution and production, where packaging, hazardous materials and supply-chain choices require careful management. STOCKMEIER’s report highlights reusable packaging, high recycling rates for several packaging materials, waste separation and the return of drum clips for reuse. Supplier sustainability is also assessed through EcoVadis and risk-management processes. This round explores how purchasing, planning, handling and disposal decisions can conserve resources, prevent pollution and support a circular economy.</t>
+  </si>
+  <si>
+    <t>Use materials and chemicals responsibly</t>
+  </si>
+  <si>
+    <t>Prevent waste through reduction and reuse</t>
+  </si>
+  <si>
+    <t>Build transparent and sustainable supply chains</t>
   </si>
   <si>
     <t>SDG 12: Verantwoorde consumptie en productie</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 12. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 12 draait om produceren en consumeren met minder grondstoffen, minder afval en beter beheer van chemicaliën gedurende hun hele levenscyclus. Het doel stimuleert efficiënt materiaalgebruik, preventie, hergebruik, recycling, verantwoord inkopen en transparante duurzaamheidsrapportage. Dit is extra relevant bij chemische distributie en productie, waar verpakkingen, gevaarlijke stoffen en ketenkeuzes zorgvuldig moeten worden beheerd. Het duurzaamheidsrapport van STOCKMEIER noemt herbruikbare verpakkingen, hoge recyclingpercentages voor verschillende verpakkingsmaterialen, afvalscheiding en retourstromen voor hergebruik van drumclips. Ook wordt duurzaamheid van leveranciers beoordeeld via EcoVadis en risicomanagement. In deze ronde ontdek je hoe beslissingen bij inkoop, planning, handling en afvalverwerking grondstoffen besparen, vervuiling voorkomen en een circulaire economie ondersteunen.</t>
+  </si>
+  <si>
+    <t>Grondstoffen en chemicaliën verantwoord gebruiken</t>
+  </si>
+  <si>
+    <t>Afval voorkomen door vermindering en hergebruik</t>
+  </si>
+  <si>
+    <t>Transparante en duurzame ketens opbouwen</t>
   </si>
   <si>
     <t>ODD 12 : Responsible Consumption and Production</t>
@@ -499,13 +661,31 @@
     <t>SDG 13: Climate Action</t>
   </si>
   <si>
-    <t>This round focuses on SDG 13. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 13 calls for urgent action against climate change and its impacts. This includes reducing greenhouse gas emissions, adapting to physical risks and improving knowledge and preparedness. For businesses, climate action covers energy, transport, products, purchasing and the resilience of sites and supply chains. STOCKMEIER calculates Scope 1, 2 and 3 emissions using the Greenhouse Gas Protocol and aims for zero carbon emissions by 2035. The report describes renewable electricity, photovoltaic projects, electric mobility and planned site-specific climate-risk analysis. It also explains risks such as flooding, heat, storms and disrupted logistics. This round explores the difference between mitigation and adaptation and shows how measurement, investment and everyday choices support a credible climate transition.</t>
+  </si>
+  <si>
+    <t>Reduce greenhouse gas emissions</t>
+  </si>
+  <si>
+    <t>Adapt to physical climate risks</t>
+  </si>
+  <si>
+    <t>Measure impact and build awareness</t>
   </si>
   <si>
     <t>SDG 13: Klimaatactie</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 13. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 13 roept op tot urgente actie tegen klimaatverandering en de gevolgen ervan. Dat betekent broeikasgasemissies verminderen, aanpassen aan fysieke risico’s en kennis en voorbereiding verbeteren. Voor bedrijven raakt klimaatactie energie, transport, producten, inkoop en de weerbaarheid van locaties en ketens. STOCKMEIER berekent Scope 1-, 2- en 3-emissies volgens het Greenhouse Gas Protocol en streeft naar nul CO₂-uitstoot in 2035. Het rapport beschrijft hernieuwbare elektriciteit, zonnepanelen, elektrische mobiliteit en geplande locatiespecifieke klimaatrisicoanalyses. Ook komen risico’s als overstromingen, hitte, stormen en logistieke verstoringen aan bod. In deze ronde ontdek je het verschil tussen emissiereductie en klimaatadaptatie en hoe meten, investeren en dagelijkse keuzes bijdragen aan een geloofwaardige klimaattransitie.</t>
+  </si>
+  <si>
+    <t>Broeikasgasemissies verminderen</t>
+  </si>
+  <si>
+    <t>Aanpassen aan fysieke klimaatrisico’s</t>
+  </si>
+  <si>
+    <t>Impact meten en bewustwording vergroten</t>
   </si>
   <si>
     <t>ODD 13 : Climate Action</t>
@@ -532,13 +712,31 @@
     <t>SDG 17: Partnerships for the Goals</t>
   </si>
   <si>
-    <t>This round focuses on SDG 17. You will discover how this global goal connects to everyday choices at work and at home, and where practical action can make a difference.</t>
+    <t>SDG 17 recognises that the Sustainable Development Goals cannot be achieved by one organisation alone. Progress depends on cooperation, shared knowledge, reliable data and partnerships across countries, sectors and supply chains. Companies can contribute by working with employees, customers, suppliers, authorities and specialist organisations on common standards and practical improvements. STOCKMEIER’s report describes a European Sustainability Taskforce, a Steering Committee, local ambassadors and collaboration with SHEQ teams. It also refers to partnerships and frameworks such as EcoVadis, ISO 14001, the Greenhouse Gas Protocol and the UN SDGs. This round explores how clear roles, transparent information and long-term cooperation help turn separate initiatives into coordinated action with greater reach and impact.</t>
+  </si>
+  <si>
+    <t>Cooperate across teams, countries and sectors</t>
+  </si>
+  <si>
+    <t>Share knowledge, data and good practices</t>
+  </si>
+  <si>
+    <t>Use common standards to accelerate progress</t>
   </si>
   <si>
     <t>SDG 17: Partnerschap om doelstellingen te bereiken</t>
   </si>
   <si>
-    <t>Deze ronde staat in het teken van SDG 17. Je ontdekt hoe dit wereldwijde doel aansluit op dagelijkse keuzes op het werk en thuis, en waar praktische actie het verschil kan maken.</t>
+    <t>SDG 17 benadrukt dat de Sustainable Development Goals niet door één organisatie alleen kunnen worden bereikt. Vooruitgang vraagt om samenwerking, kennisdeling, betrouwbare gegevens en partnerschappen tussen landen, sectoren en ketenpartners. Bedrijven kunnen bijdragen door met medewerkers, klanten, leveranciers, overheden en gespecialiseerde organisaties te werken aan gezamenlijke normen en praktische verbeteringen. Het duurzaamheidsrapport van STOCKMEIER beschrijft een Europese Sustainability Taskforce, een Steering Committee, lokale ambassadeurs en samenwerking met SHEQ-teams. Ook worden kaders en partners genoemd zoals EcoVadis, ISO 14001, het Greenhouse Gas Protocol en de VN-SDG’s. In deze ronde ontdek je hoe duidelijke rollen, transparante informatie en langdurige samenwerking losse initiatieven veranderen in gecoördineerde actie met een groter bereik en effect.</t>
+  </si>
+  <si>
+    <t>Samenwerken tussen teams, landen en sectoren</t>
+  </si>
+  <si>
+    <t>Kennis, gegevens en goede praktijken delen</t>
+  </si>
+  <si>
+    <t>Gezamenlijke standaarden gebruiken voor versnelling</t>
   </si>
   <si>
     <t>ODD 17 : Partnerships for the Goals</t>
@@ -865,7 +1063,7 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
+    <col min="5" max="5" width="78" customWidth="1"/>
     <col min="6" max="8" width="34" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
@@ -899,7 +1097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="44.1" customHeight="1">
+    <row r="2" spans="1:9" ht="87.95" customHeight="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -928,7 +1126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="44.1" customHeight="1">
+    <row r="3" spans="1:9" ht="87.95" customHeight="1">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -957,7 +1155,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="44.1" customHeight="1">
+    <row r="4" spans="1:9" ht="87.95" customHeight="1">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -986,7 +1184,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="44.1" customHeight="1">
+    <row r="5" spans="1:9" ht="87.95" customHeight="1">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1015,7 +1213,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="44.1" customHeight="1">
+    <row r="6" spans="1:9" ht="87.95" customHeight="1">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -1044,7 +1242,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="44.1" customHeight="1">
+    <row r="7" spans="1:9" ht="87.95" customHeight="1">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -1073,7 +1271,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="44.1" customHeight="1">
+    <row r="8" spans="1:9" ht="87.95" customHeight="1">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -1102,7 +1300,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="44.1" customHeight="1">
+    <row r="9" spans="1:9" ht="87.95" customHeight="1">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -1119,19 +1317,19 @@
         <v>56</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="44.1" customHeight="1">
+    <row r="10" spans="1:9" ht="87.95" customHeight="1">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -1142,25 +1340,25 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="44.1" customHeight="1">
+    <row r="11" spans="1:9" ht="87.95" customHeight="1">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -1171,10 +1369,10 @@
         <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>26</v>
@@ -1189,7 +1387,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="44.1" customHeight="1">
+    <row r="12" spans="1:9" ht="87.95" customHeight="1">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -1203,7 +1401,7 @@
         <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>32</v>
@@ -1218,7 +1416,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="44.1" customHeight="1">
+    <row r="13" spans="1:9" ht="87.95" customHeight="1">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -1229,10 +1427,10 @@
         <v>36</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>39</v>
@@ -1247,7 +1445,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="44.1" customHeight="1">
+    <row r="14" spans="1:9" ht="87.95" customHeight="1">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -1261,7 +1459,7 @@
         <v>55</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>45</v>
@@ -1276,7 +1474,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="44.1" customHeight="1">
+    <row r="15" spans="1:9" ht="87.95" customHeight="1">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1290,7 +1488,7 @@
         <v>55</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>51</v>
@@ -1305,7 +1503,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="44.1" customHeight="1">
+    <row r="16" spans="1:9" ht="87.95" customHeight="1">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1316,25 +1514,25 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="44.1" customHeight="1">
+    <row r="17" spans="1:9" ht="87.95" customHeight="1">
       <c r="A17" s="3">
         <v>3</v>
       </c>
@@ -1345,25 +1543,25 @@
         <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="44.1" customHeight="1">
+    <row r="18" spans="1:9" ht="87.95" customHeight="1">
       <c r="A18" s="3">
         <v>3</v>
       </c>
@@ -1374,10 +1572,10 @@
         <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>26</v>
@@ -1392,7 +1590,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="44.1" customHeight="1">
+    <row r="19" spans="1:9" ht="87.95" customHeight="1">
       <c r="A19" s="3">
         <v>3</v>
       </c>
@@ -1403,10 +1601,10 @@
         <v>30</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>32</v>
@@ -1421,7 +1619,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="44.1" customHeight="1">
+    <row r="20" spans="1:9" ht="87.95" customHeight="1">
       <c r="A20" s="3">
         <v>3</v>
       </c>
@@ -1432,10 +1630,10 @@
         <v>36</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>39</v>
@@ -1450,7 +1648,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="44.1" customHeight="1">
+    <row r="21" spans="1:9" ht="87.95" customHeight="1">
       <c r="A21" s="3">
         <v>3</v>
       </c>
@@ -1461,10 +1659,10 @@
         <v>43</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>45</v>
@@ -1479,7 +1677,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="44.1" customHeight="1">
+    <row r="22" spans="1:9" ht="87.95" customHeight="1">
       <c r="A22" s="3">
         <v>3</v>
       </c>
@@ -1490,10 +1688,10 @@
         <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>51</v>
@@ -1508,7 +1706,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="44.1" customHeight="1">
+    <row r="23" spans="1:9" ht="87.95" customHeight="1">
       <c r="A23" s="3">
         <v>4</v>
       </c>
@@ -1519,25 +1717,25 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="44.1" customHeight="1">
+    <row r="24" spans="1:9" ht="87.95" customHeight="1">
       <c r="A24" s="3">
         <v>4</v>
       </c>
@@ -1548,25 +1746,25 @@
         <v>16</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="44.1" customHeight="1">
+    <row r="25" spans="1:9" ht="87.95" customHeight="1">
       <c r="A25" s="3">
         <v>4</v>
       </c>
@@ -1577,10 +1775,10 @@
         <v>23</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>26</v>
@@ -1595,7 +1793,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="44.1" customHeight="1">
+    <row r="26" spans="1:9" ht="87.95" customHeight="1">
       <c r="A26" s="3">
         <v>4</v>
       </c>
@@ -1606,10 +1804,10 @@
         <v>30</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>32</v>
@@ -1624,7 +1822,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="44.1" customHeight="1">
+    <row r="27" spans="1:9" ht="87.95" customHeight="1">
       <c r="A27" s="3">
         <v>4</v>
       </c>
@@ -1635,10 +1833,10 @@
         <v>36</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>39</v>
@@ -1653,7 +1851,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="44.1" customHeight="1">
+    <row r="28" spans="1:9" ht="87.95" customHeight="1">
       <c r="A28" s="3">
         <v>4</v>
       </c>
@@ -1664,10 +1862,10 @@
         <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>45</v>
@@ -1682,7 +1880,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="44.1" customHeight="1">
+    <row r="29" spans="1:9" ht="87.95" customHeight="1">
       <c r="A29" s="3">
         <v>4</v>
       </c>
@@ -1693,10 +1891,10 @@
         <v>49</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>51</v>
@@ -1711,7 +1909,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="44.1" customHeight="1">
+    <row r="30" spans="1:9" ht="87.95" customHeight="1">
       <c r="A30" s="3">
         <v>5</v>
       </c>
@@ -1722,25 +1920,25 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="44.1" customHeight="1">
+    <row r="31" spans="1:9" ht="87.95" customHeight="1">
       <c r="A31" s="3">
         <v>5</v>
       </c>
@@ -1751,25 +1949,25 @@
         <v>16</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="44.1" customHeight="1">
+    <row r="32" spans="1:9" ht="87.95" customHeight="1">
       <c r="A32" s="3">
         <v>5</v>
       </c>
@@ -1780,10 +1978,10 @@
         <v>23</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>26</v>
@@ -1798,7 +1996,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="44.1" customHeight="1">
+    <row r="33" spans="1:9" ht="87.95" customHeight="1">
       <c r="A33" s="3">
         <v>5</v>
       </c>
@@ -1809,10 +2007,10 @@
         <v>30</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>32</v>
@@ -1827,7 +2025,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="44.1" customHeight="1">
+    <row r="34" spans="1:9" ht="87.95" customHeight="1">
       <c r="A34" s="3">
         <v>5</v>
       </c>
@@ -1838,10 +2036,10 @@
         <v>36</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>39</v>
@@ -1856,7 +2054,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="44.1" customHeight="1">
+    <row r="35" spans="1:9" ht="87.95" customHeight="1">
       <c r="A35" s="3">
         <v>5</v>
       </c>
@@ -1867,10 +2065,10 @@
         <v>43</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>45</v>
@@ -1885,7 +2083,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="44.1" customHeight="1">
+    <row r="36" spans="1:9" ht="87.95" customHeight="1">
       <c r="A36" s="3">
         <v>5</v>
       </c>
@@ -1896,10 +2094,10 @@
         <v>49</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>51</v>
@@ -1914,7 +2112,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="44.1" customHeight="1">
+    <row r="37" spans="1:9" ht="87.95" customHeight="1">
       <c r="A37" s="3">
         <v>6</v>
       </c>
@@ -1925,25 +2123,25 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="44.1" customHeight="1">
+    <row r="38" spans="1:9" ht="87.95" customHeight="1">
       <c r="A38" s="3">
         <v>6</v>
       </c>
@@ -1954,25 +2152,25 @@
         <v>16</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="44.1" customHeight="1">
+    <row r="39" spans="1:9" ht="87.95" customHeight="1">
       <c r="A39" s="3">
         <v>6</v>
       </c>
@@ -1983,10 +2181,10 @@
         <v>23</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>26</v>
@@ -2001,7 +2199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="44.1" customHeight="1">
+    <row r="40" spans="1:9" ht="87.95" customHeight="1">
       <c r="A40" s="3">
         <v>6</v>
       </c>
@@ -2012,10 +2210,10 @@
         <v>30</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>32</v>
@@ -2030,7 +2228,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="44.1" customHeight="1">
+    <row r="41" spans="1:9" ht="87.95" customHeight="1">
       <c r="A41" s="3">
         <v>6</v>
       </c>
@@ -2041,10 +2239,10 @@
         <v>36</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>39</v>
@@ -2059,7 +2257,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="44.1" customHeight="1">
+    <row r="42" spans="1:9" ht="87.95" customHeight="1">
       <c r="A42" s="3">
         <v>6</v>
       </c>
@@ -2070,10 +2268,10 @@
         <v>43</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>45</v>
@@ -2088,7 +2286,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="44.1" customHeight="1">
+    <row r="43" spans="1:9" ht="87.95" customHeight="1">
       <c r="A43" s="3">
         <v>6</v>
       </c>
@@ -2099,10 +2297,10 @@
         <v>49</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>51</v>
@@ -2117,7 +2315,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="44.1" customHeight="1">
+    <row r="44" spans="1:9" ht="87.95" customHeight="1">
       <c r="A44" s="3">
         <v>7</v>
       </c>
@@ -2128,25 +2326,25 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="44.1" customHeight="1">
+    <row r="45" spans="1:9" ht="87.95" customHeight="1">
       <c r="A45" s="3">
         <v>7</v>
       </c>
@@ -2157,25 +2355,25 @@
         <v>16</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="44.1" customHeight="1">
+    <row r="46" spans="1:9" ht="87.95" customHeight="1">
       <c r="A46" s="3">
         <v>7</v>
       </c>
@@ -2186,10 +2384,10 @@
         <v>23</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>26</v>
@@ -2204,7 +2402,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="44.1" customHeight="1">
+    <row r="47" spans="1:9" ht="87.95" customHeight="1">
       <c r="A47" s="3">
         <v>7</v>
       </c>
@@ -2215,10 +2413,10 @@
         <v>30</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>32</v>
@@ -2233,7 +2431,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="44.1" customHeight="1">
+    <row r="48" spans="1:9" ht="87.95" customHeight="1">
       <c r="A48" s="3">
         <v>7</v>
       </c>
@@ -2244,10 +2442,10 @@
         <v>36</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>39</v>
@@ -2262,7 +2460,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="44.1" customHeight="1">
+    <row r="49" spans="1:9" ht="87.95" customHeight="1">
       <c r="A49" s="3">
         <v>7</v>
       </c>
@@ -2273,10 +2471,10 @@
         <v>43</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>45</v>
@@ -2291,7 +2489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="44.1" customHeight="1">
+    <row r="50" spans="1:9" ht="87.95" customHeight="1">
       <c r="A50" s="3">
         <v>7</v>
       </c>
@@ -2302,10 +2500,10 @@
         <v>49</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>51</v>
@@ -2320,7 +2518,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="44.1" customHeight="1">
+    <row r="51" spans="1:9" ht="87.95" customHeight="1">
       <c r="A51" s="3">
         <v>8</v>
       </c>
@@ -2331,25 +2529,25 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="44.1" customHeight="1">
+    <row r="52" spans="1:9" ht="87.95" customHeight="1">
       <c r="A52" s="3">
         <v>8</v>
       </c>
@@ -2360,25 +2558,25 @@
         <v>16</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="44.1" customHeight="1">
+    <row r="53" spans="1:9" ht="87.95" customHeight="1">
       <c r="A53" s="3">
         <v>8</v>
       </c>
@@ -2389,10 +2587,10 @@
         <v>23</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>26</v>
@@ -2407,7 +2605,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="44.1" customHeight="1">
+    <row r="54" spans="1:9" ht="87.95" customHeight="1">
       <c r="A54" s="3">
         <v>8</v>
       </c>
@@ -2418,10 +2616,10 @@
         <v>30</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>32</v>
@@ -2436,7 +2634,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="44.1" customHeight="1">
+    <row r="55" spans="1:9" ht="87.95" customHeight="1">
       <c r="A55" s="3">
         <v>8</v>
       </c>
@@ -2447,10 +2645,10 @@
         <v>36</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>39</v>
@@ -2465,7 +2663,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="44.1" customHeight="1">
+    <row r="56" spans="1:9" ht="87.95" customHeight="1">
       <c r="A56" s="3">
         <v>8</v>
       </c>
@@ -2476,10 +2674,10 @@
         <v>43</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>45</v>
@@ -2494,7 +2692,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="44.1" customHeight="1">
+    <row r="57" spans="1:9" ht="87.95" customHeight="1">
       <c r="A57" s="3">
         <v>8</v>
       </c>
@@ -2505,10 +2703,10 @@
         <v>49</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>51</v>
@@ -2523,7 +2721,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="44.1" customHeight="1">
+    <row r="58" spans="1:9" ht="87.95" customHeight="1">
       <c r="A58" s="3">
         <v>9</v>
       </c>
@@ -2534,25 +2732,25 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>14</v>
+        <v>178</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="44.1" customHeight="1">
+    <row r="59" spans="1:9" ht="87.95" customHeight="1">
       <c r="A59" s="3">
         <v>9</v>
       </c>
@@ -2563,25 +2761,25 @@
         <v>16</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="44.1" customHeight="1">
+    <row r="60" spans="1:9" ht="87.95" customHeight="1">
       <c r="A60" s="3">
         <v>9</v>
       </c>
@@ -2592,10 +2790,10 @@
         <v>23</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>26</v>
@@ -2610,7 +2808,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="44.1" customHeight="1">
+    <row r="61" spans="1:9" ht="87.95" customHeight="1">
       <c r="A61" s="3">
         <v>9</v>
       </c>
@@ -2621,10 +2819,10 @@
         <v>30</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>32</v>
@@ -2639,7 +2837,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="44.1" customHeight="1">
+    <row r="62" spans="1:9" ht="87.95" customHeight="1">
       <c r="A62" s="3">
         <v>9</v>
       </c>
@@ -2650,10 +2848,10 @@
         <v>36</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>39</v>
@@ -2668,7 +2866,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="44.1" customHeight="1">
+    <row r="63" spans="1:9" ht="87.95" customHeight="1">
       <c r="A63" s="3">
         <v>9</v>
       </c>
@@ -2679,10 +2877,10 @@
         <v>43</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>45</v>
@@ -2697,7 +2895,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="44.1" customHeight="1">
+    <row r="64" spans="1:9" ht="87.95" customHeight="1">
       <c r="A64" s="3">
         <v>9</v>
       </c>
@@ -2708,10 +2906,10 @@
         <v>49</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>51</v>
@@ -2726,7 +2924,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="44.1" customHeight="1">
+    <row r="65" spans="1:9" ht="87.95" customHeight="1">
       <c r="A65" s="3">
         <v>10</v>
       </c>
@@ -2737,25 +2935,25 @@
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>12</v>
+        <v>193</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>14</v>
+        <v>195</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="44.1" customHeight="1">
+    <row r="66" spans="1:9" ht="87.95" customHeight="1">
       <c r="A66" s="3">
         <v>10</v>
       </c>
@@ -2766,25 +2964,25 @@
         <v>16</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="44.1" customHeight="1">
+    <row r="67" spans="1:9" ht="87.95" customHeight="1">
       <c r="A67" s="3">
         <v>10</v>
       </c>
@@ -2795,10 +2993,10 @@
         <v>23</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>26</v>
@@ -2813,7 +3011,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="44.1" customHeight="1">
+    <row r="68" spans="1:9" ht="87.95" customHeight="1">
       <c r="A68" s="3">
         <v>10</v>
       </c>
@@ -2824,10 +3022,10 @@
         <v>30</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>32</v>
@@ -2842,7 +3040,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="44.1" customHeight="1">
+    <row r="69" spans="1:9" ht="87.95" customHeight="1">
       <c r="A69" s="3">
         <v>10</v>
       </c>
@@ -2853,10 +3051,10 @@
         <v>36</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>39</v>
@@ -2871,7 +3069,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="44.1" customHeight="1">
+    <row r="70" spans="1:9" ht="87.95" customHeight="1">
       <c r="A70" s="3">
         <v>10</v>
       </c>
@@ -2882,10 +3080,10 @@
         <v>43</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>45</v>
@@ -2900,7 +3098,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="44.1" customHeight="1">
+    <row r="71" spans="1:9" ht="87.95" customHeight="1">
       <c r="A71" s="3">
         <v>10</v>
       </c>
@@ -2911,10 +3109,10 @@
         <v>49</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>51</v>
@@ -2929,7 +3127,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="44.1" customHeight="1">
+    <row r="72" spans="1:9" ht="87.95" customHeight="1">
       <c r="A72" s="3">
         <v>11</v>
       </c>
@@ -2940,25 +3138,25 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>12</v>
+        <v>210</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>14</v>
+        <v>212</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="44.1" customHeight="1">
+    <row r="73" spans="1:9" ht="87.95" customHeight="1">
       <c r="A73" s="3">
         <v>11</v>
       </c>
@@ -2969,25 +3167,25 @@
         <v>16</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>156</v>
+        <v>213</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>19</v>
+        <v>215</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="44.1" customHeight="1">
+    <row r="74" spans="1:9" ht="87.95" customHeight="1">
       <c r="A74" s="3">
         <v>11</v>
       </c>
@@ -2998,10 +3196,10 @@
         <v>23</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>26</v>
@@ -3016,7 +3214,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="44.1" customHeight="1">
+    <row r="75" spans="1:9" ht="87.95" customHeight="1">
       <c r="A75" s="3">
         <v>11</v>
       </c>
@@ -3027,10 +3225,10 @@
         <v>30</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>32</v>
@@ -3045,7 +3243,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="44.1" customHeight="1">
+    <row r="76" spans="1:9" ht="87.95" customHeight="1">
       <c r="A76" s="3">
         <v>11</v>
       </c>
@@ -3056,10 +3254,10 @@
         <v>36</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>162</v>
+        <v>222</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>39</v>
@@ -3074,7 +3272,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="44.1" customHeight="1">
+    <row r="77" spans="1:9" ht="87.95" customHeight="1">
       <c r="A77" s="3">
         <v>11</v>
       </c>
@@ -3085,10 +3283,10 @@
         <v>43</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>45</v>
@@ -3103,7 +3301,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="44.1" customHeight="1">
+    <row r="78" spans="1:9" ht="87.95" customHeight="1">
       <c r="A78" s="3">
         <v>11</v>
       </c>
@@ -3114,10 +3312,10 @@
         <v>49</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>51</v>
@@ -3132,7 +3330,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="44.1" customHeight="1">
+    <row r="79" spans="1:9" ht="87.95" customHeight="1">
       <c r="A79" s="3">
         <v>12</v>
       </c>
@@ -3143,25 +3341,25 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>166</v>
+        <v>226</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>12</v>
+        <v>227</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>13</v>
+        <v>228</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="44.1" customHeight="1">
+    <row r="80" spans="1:9" ht="87.95" customHeight="1">
       <c r="A80" s="3">
         <v>12</v>
       </c>
@@ -3172,25 +3370,25 @@
         <v>16</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>167</v>
+        <v>230</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>168</v>
+        <v>231</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="44.1" customHeight="1">
+    <row r="81" spans="1:9" ht="87.95" customHeight="1">
       <c r="A81" s="3">
         <v>12</v>
       </c>
@@ -3201,10 +3399,10 @@
         <v>23</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>169</v>
+        <v>235</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>170</v>
+        <v>236</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>26</v>
@@ -3219,7 +3417,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="44.1" customHeight="1">
+    <row r="82" spans="1:9" ht="87.95" customHeight="1">
       <c r="A82" s="3">
         <v>12</v>
       </c>
@@ -3230,10 +3428,10 @@
         <v>30</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>32</v>
@@ -3248,7 +3446,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="44.1" customHeight="1">
+    <row r="83" spans="1:9" ht="87.95" customHeight="1">
       <c r="A83" s="3">
         <v>12</v>
       </c>
@@ -3259,10 +3457,10 @@
         <v>36</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>39</v>
@@ -3277,7 +3475,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="44.1" customHeight="1">
+    <row r="84" spans="1:9" ht="87.95" customHeight="1">
       <c r="A84" s="3">
         <v>12</v>
       </c>
@@ -3288,10 +3486,10 @@
         <v>43</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>45</v>
@@ -3306,7 +3504,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="44.1" customHeight="1">
+    <row r="85" spans="1:9" ht="87.95" customHeight="1">
       <c r="A85" s="3">
         <v>12</v>
       </c>
@@ -3317,10 +3515,10 @@
         <v>49</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>51</v>
@@ -3354,7 +3552,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="32.1" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="6"/>
@@ -3362,50 +3560,50 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>178</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="B4" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
